--- a/back-end/Intermediate_data/user_uTest2/sixth/output/智能鉴定与三维全参数矩阵.xlsx
+++ b/back-end/Intermediate_data/user_uTest2/sixth/output/智能鉴定与三维全参数矩阵.xlsx
@@ -508,7 +508,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>189</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2.6e-05</v>
+        <v>0.005003</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>12106.552052</v>
+        <v>14220.383821</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>12807.021515</v>
+        <v>14685.004067</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>12106.552052</v>
+        <v>75.240126</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>12106.552052</v>
+        <v>0.106259</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>12807.021515</v>
+        <v>77.69843400000001</v>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>12807.021515</v>
+        <v>0.003999</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>28.488786</v>
+        <v>1.927735</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>28.488786</v>
+        <v>0.587654</v>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.19909</v>
+        <v>337.425317</v>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>0.19909</v>
+        <v>12.031188</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0.320482</v>
+        <v>795222.155427</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>0.320482</v>
+        <v>10776.558827</v>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.320482</v>
+        <v>0.162109</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>2.026407</v>
+        <v>6937.787521</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>2.026407</v>
+        <v>118.026371</v>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>2.026407</v>
+        <v>1.13647</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>26.485069</v>
+        <v>1.395318</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>26.485069</v>
+        <v>0.098523</v>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>29.874164</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>0</v>
+        <v>21.6686</v>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>100</v>
+        <v>85.135199</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>11.674782</v>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>0</v>
+        <v>0.971181</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>1</v>
+        <v>26.484783</v>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         </is>
       </c>
       <c r="B43" s="6" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>一次短路</t>
+          <t>二次短路</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
@@ -1112,7 +1112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1191,6 +1191,5458 @@
         <v>0</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B3" t="n">
+        <v>457.113506</v>
+      </c>
+      <c r="C3" t="n">
+        <v>45.921701</v>
+      </c>
+      <c r="D3" t="n">
+        <v>9.557445</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6.249072</v>
+      </c>
+      <c r="F3" t="n">
+        <v>9.218413</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3.471335</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3.678096</v>
+      </c>
+      <c r="I3" t="n">
+        <v>26.954521</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="n">
+        <v>197.261387</v>
+      </c>
+      <c r="C4" t="n">
+        <v>311.603125</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7.222394</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.525909</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.214997</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.912263</v>
+      </c>
+      <c r="H4" t="n">
+        <v>8.106896000000001</v>
+      </c>
+      <c r="I4" t="n">
+        <v>11.80847</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B5" t="n">
+        <v>159.223816</v>
+      </c>
+      <c r="C5" t="n">
+        <v>14.26402</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.724652</v>
+      </c>
+      <c r="E5" t="n">
+        <v>9.959728999999999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>18.290751</v>
+      </c>
+      <c r="G5" t="n">
+        <v>6.792789</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.344059</v>
+      </c>
+      <c r="I5" t="n">
+        <v>20.803002</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>37</v>
+      </c>
+      <c r="B6" t="n">
+        <v>105.664205</v>
+      </c>
+      <c r="C6" t="n">
+        <v>13.757503</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5.865564</v>
+      </c>
+      <c r="E6" t="n">
+        <v>7.856512</v>
+      </c>
+      <c r="F6" t="n">
+        <v>18.107078</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3.979652</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.252204</v>
+      </c>
+      <c r="I6" t="n">
+        <v>24.275751</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B7" t="n">
+        <v>105.378186</v>
+      </c>
+      <c r="C7" t="n">
+        <v>40.398548</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5.860266</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2.670661</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3.176728</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.640113</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.119765</v>
+      </c>
+      <c r="I7" t="n">
+        <v>27.687248</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>45</v>
+      </c>
+      <c r="B8" t="n">
+        <v>88.078794</v>
+      </c>
+      <c r="C8" t="n">
+        <v>9.200697</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5.520235</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10.405053</v>
+      </c>
+      <c r="F8" t="n">
+        <v>18.676538</v>
+      </c>
+      <c r="G8" t="n">
+        <v>9.083688</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.092732</v>
+      </c>
+      <c r="I8" t="n">
+        <v>24.394709</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" t="n">
+        <v>84.53241800000001</v>
+      </c>
+      <c r="C9" t="n">
+        <v>149.854776</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5.44513</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.621578</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.216974</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.186002</v>
+      </c>
+      <c r="H9" t="n">
+        <v>6.252185</v>
+      </c>
+      <c r="I9" t="n">
+        <v>15.135647</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79.526385</v>
+      </c>
+      <c r="C10" t="n">
+        <v>38.835321</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5.335448</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.302845</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.39812</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.843243</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.140998</v>
+      </c>
+      <c r="I10" t="n">
+        <v>26.595764</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>34</v>
+      </c>
+      <c r="B11" t="n">
+        <v>64.814297</v>
+      </c>
+      <c r="C11" t="n">
+        <v>14.073479</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.983763</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5.54451</v>
+      </c>
+      <c r="F11" t="n">
+        <v>7.005655</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.779242</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.44622</v>
+      </c>
+      <c r="I11" t="n">
+        <v>24.134123</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" t="n">
+        <v>51.72915</v>
+      </c>
+      <c r="C12" t="n">
+        <v>125.173713</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4.622876</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.536366</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.165614</v>
+      </c>
+      <c r="G12" t="n">
+        <v>6.508118</v>
+      </c>
+      <c r="H12" t="n">
+        <v>9.206839</v>
+      </c>
+      <c r="I12" t="n">
+        <v>18.927174</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>104</v>
+      </c>
+      <c r="B13" t="n">
+        <v>40.653219</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2.539853</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4.266111</v>
+      </c>
+      <c r="E13" t="n">
+        <v>22.511552</v>
+      </c>
+      <c r="F13" t="n">
+        <v>54.477359</v>
+      </c>
+      <c r="G13" t="n">
+        <v>23.329777</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.869723</v>
+      </c>
+      <c r="I13" t="n">
+        <v>23.014954</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>92</v>
+      </c>
+      <c r="B14" t="n">
+        <v>35.610232</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.310413</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4.081866</v>
+      </c>
+      <c r="E14" t="n">
+        <v>15.811938</v>
+      </c>
+      <c r="F14" t="n">
+        <v>41.013279</v>
+      </c>
+      <c r="G14" t="n">
+        <v>7.165425</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.094795</v>
+      </c>
+      <c r="I14" t="n">
+        <v>20.735337</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>78</v>
+      </c>
+      <c r="B15" t="n">
+        <v>32.364749</v>
+      </c>
+      <c r="C15" t="n">
+        <v>5.059565</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3.95389</v>
+      </c>
+      <c r="E15" t="n">
+        <v>9.707018</v>
+      </c>
+      <c r="F15" t="n">
+        <v>16.780736</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.97123</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.929601</v>
+      </c>
+      <c r="I15" t="n">
+        <v>27.514537</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>26</v>
+      </c>
+      <c r="B16" t="n">
+        <v>29.662889</v>
+      </c>
+      <c r="C16" t="n">
+        <v>13.575802</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3.840652</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3.413456</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.607504</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.074687</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.738525</v>
+      </c>
+      <c r="I16" t="n">
+        <v>26.093191</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B17" t="n">
+        <v>25.393381</v>
+      </c>
+      <c r="C17" t="n">
+        <v>57.094152</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3.646761</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.7317669999999999</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.300591</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.940427</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3.655315</v>
+      </c>
+      <c r="I17" t="n">
+        <v>12.570179</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>97</v>
+      </c>
+      <c r="B18" t="n">
+        <v>23.25249</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2.5801</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3.541253</v>
+      </c>
+      <c r="E18" t="n">
+        <v>15.269583</v>
+      </c>
+      <c r="F18" t="n">
+        <v>53.94436</v>
+      </c>
+      <c r="G18" t="n">
+        <v>8.043692999999999</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.013943</v>
+      </c>
+      <c r="I18" t="n">
+        <v>22.532009</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>139</v>
+      </c>
+      <c r="B19" t="n">
+        <v>22.62349</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1.97101</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3.509029</v>
+      </c>
+      <c r="E19" t="n">
+        <v>19.626149</v>
+      </c>
+      <c r="F19" t="n">
+        <v>38.311399</v>
+      </c>
+      <c r="G19" t="n">
+        <v>9.078792</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.037186</v>
+      </c>
+      <c r="I19" t="n">
+        <v>24.566729</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>9</v>
+      </c>
+      <c r="B20" t="n">
+        <v>22.540533</v>
+      </c>
+      <c r="C20" t="n">
+        <v>44.360335</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3.504735</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.869892</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.300025</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.319273</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.515475</v>
+      </c>
+      <c r="I20" t="n">
+        <v>26.443761</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>68</v>
+      </c>
+      <c r="B21" t="n">
+        <v>22.426041</v>
+      </c>
+      <c r="C21" t="n">
+        <v>5.799814</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3.498791</v>
+      </c>
+      <c r="E21" t="n">
+        <v>6.630889</v>
+      </c>
+      <c r="F21" t="n">
+        <v>7.758861</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.752024</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.149501</v>
+      </c>
+      <c r="I21" t="n">
+        <v>22.385848</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>148</v>
+      </c>
+      <c r="B22" t="n">
+        <v>20.567486</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1.493098</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3.399337</v>
+      </c>
+      <c r="E22" t="n">
+        <v>24.313637</v>
+      </c>
+      <c r="F22" t="n">
+        <v>77.380449</v>
+      </c>
+      <c r="G22" t="n">
+        <v>13.682388</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.095149</v>
+      </c>
+      <c r="I22" t="n">
+        <v>26.087143</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>6</v>
+      </c>
+      <c r="B23" t="n">
+        <v>17.13753</v>
+      </c>
+      <c r="C23" t="n">
+        <v>50.849019</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3.198771</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.63217</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.276411</v>
+      </c>
+      <c r="G23" t="n">
+        <v>5.226992</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4.752381</v>
+      </c>
+      <c r="I23" t="n">
+        <v>13.55255</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" t="n">
+        <v>16.645863</v>
+      </c>
+      <c r="C24" t="n">
+        <v>46.933492</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3.167884</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.671747</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.296498</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3.594659</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4.107374</v>
+      </c>
+      <c r="I24" t="n">
+        <v>21.550565</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>15</v>
+      </c>
+      <c r="B25" t="n">
+        <v>16.594257</v>
+      </c>
+      <c r="C25" t="n">
+        <v>38.29815</v>
+      </c>
+      <c r="D25" t="n">
+        <v>3.164607</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.821507</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.474621</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3.026457</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2.805423</v>
+      </c>
+      <c r="I25" t="n">
+        <v>27.000654</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>12</v>
+      </c>
+      <c r="B26" t="n">
+        <v>16.479604</v>
+      </c>
+      <c r="C26" t="n">
+        <v>36.538339</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3.157301</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.8571029999999999</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.41252</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.233055</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.066234</v>
+      </c>
+      <c r="I26" t="n">
+        <v>22.571415</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>84</v>
+      </c>
+      <c r="B27" t="n">
+        <v>16.039279</v>
+      </c>
+      <c r="C27" t="n">
+        <v>4.319419</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3.128927</v>
+      </c>
+      <c r="E27" t="n">
+        <v>7.120581</v>
+      </c>
+      <c r="F27" t="n">
+        <v>13.759197</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3.641487</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.190648</v>
+      </c>
+      <c r="I27" t="n">
+        <v>18.628493</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>10</v>
+      </c>
+      <c r="B28" t="n">
+        <v>14.829019</v>
+      </c>
+      <c r="C28" t="n">
+        <v>33.864538</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3.048161</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.861947</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.469673</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.427573</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3.158419</v>
+      </c>
+      <c r="I28" t="n">
+        <v>22.558971</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>156</v>
+      </c>
+      <c r="B29" t="n">
+        <v>14.292395</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1.052305</v>
+      </c>
+      <c r="D29" t="n">
+        <v>3.01094</v>
+      </c>
+      <c r="E29" t="n">
+        <v>27.065284</v>
+      </c>
+      <c r="F29" t="n">
+        <v>122.458776</v>
+      </c>
+      <c r="G29" t="n">
+        <v>7.892662</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.718305</v>
+      </c>
+      <c r="I29" t="n">
+        <v>18.863029</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>107</v>
+      </c>
+      <c r="B30" t="n">
+        <v>12.39368</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1.680892</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2.871225</v>
+      </c>
+      <c r="E30" t="n">
+        <v>15.407935</v>
+      </c>
+      <c r="F30" t="n">
+        <v>10.239965</v>
+      </c>
+      <c r="G30" t="n">
+        <v>12.286693</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.404047</v>
+      </c>
+      <c r="I30" t="n">
+        <v>25.382845</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>39</v>
+      </c>
+      <c r="B31" t="n">
+        <v>11.870354</v>
+      </c>
+      <c r="C31" t="n">
+        <v>11.563269</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2.83023</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2.176269</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.154662</v>
+      </c>
+      <c r="G31" t="n">
+        <v>5.697237</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2.947435</v>
+      </c>
+      <c r="I31" t="n">
+        <v>27.170204</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>13</v>
+      </c>
+      <c r="B32" t="n">
+        <v>11.805493</v>
+      </c>
+      <c r="C32" t="n">
+        <v>34.445209</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2.825065</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.727911</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.292607</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2.49896</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3.238731</v>
+      </c>
+      <c r="I32" t="n">
+        <v>23.078536</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>69</v>
+      </c>
+      <c r="B33" t="n">
+        <v>10.929137</v>
+      </c>
+      <c r="C33" t="n">
+        <v>5.974946</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2.753356</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3.986031</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.881826</v>
+      </c>
+      <c r="G33" t="n">
+        <v>4.303161</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2.07986</v>
+      </c>
+      <c r="I33" t="n">
+        <v>26.032296</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>130</v>
+      </c>
+      <c r="B34" t="n">
+        <v>9.819298</v>
+      </c>
+      <c r="C34" t="n">
+        <v>2.109836</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2.656811</v>
+      </c>
+      <c r="E34" t="n">
+        <v>10.510478</v>
+      </c>
+      <c r="F34" t="n">
+        <v>16.643648</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2.477297</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.638096</v>
+      </c>
+      <c r="I34" t="n">
+        <v>20.19806</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>16</v>
+      </c>
+      <c r="B35" t="n">
+        <v>8.866963</v>
+      </c>
+      <c r="C35" t="n">
+        <v>30.13583</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2.567983</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.687465</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.33235</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3.871858</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2.806371</v>
+      </c>
+      <c r="I35" t="n">
+        <v>21.728718</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>157</v>
+      </c>
+      <c r="B36" t="n">
+        <v>8.755312</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.966354</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2.557159</v>
+      </c>
+      <c r="E36" t="n">
+        <v>21.258322</v>
+      </c>
+      <c r="F36" t="n">
+        <v>87.209586</v>
+      </c>
+      <c r="G36" t="n">
+        <v>7.241049</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.615275</v>
+      </c>
+      <c r="I36" t="n">
+        <v>18.242672</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>154</v>
+      </c>
+      <c r="B37" t="n">
+        <v>8.377592999999999</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1.080949</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2.519843</v>
+      </c>
+      <c r="E37" t="n">
+        <v>18.454053</v>
+      </c>
+      <c r="F37" t="n">
+        <v>57.7904</v>
+      </c>
+      <c r="G37" t="n">
+        <v>5.277518</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.774493</v>
+      </c>
+      <c r="I37" t="n">
+        <v>27.77711</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>170</v>
+      </c>
+      <c r="B38" t="n">
+        <v>8.256228</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.534084</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2.507616</v>
+      </c>
+      <c r="E38" t="n">
+        <v>36.988098</v>
+      </c>
+      <c r="F38" t="n">
+        <v>154.585641</v>
+      </c>
+      <c r="G38" t="n">
+        <v>4.206211</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.381423</v>
+      </c>
+      <c r="I38" t="n">
+        <v>25.405077</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>14</v>
+      </c>
+      <c r="B39" t="n">
+        <v>8.009492</v>
+      </c>
+      <c r="C39" t="n">
+        <v>25.486682</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2.482383</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.759581</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.350179</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2.373059</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2.46458</v>
+      </c>
+      <c r="I39" t="n">
+        <v>25.254854</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>88</v>
+      </c>
+      <c r="B40" t="n">
+        <v>7.966502</v>
+      </c>
+      <c r="C40" t="n">
+        <v>3.532815</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2.477934</v>
+      </c>
+      <c r="E40" t="n">
+        <v>5.460198</v>
+      </c>
+      <c r="F40" t="n">
+        <v>8.094877</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2.211994</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.966916</v>
+      </c>
+      <c r="I40" t="n">
+        <v>24.313631</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>151</v>
+      </c>
+      <c r="B41" t="n">
+        <v>7.65728</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.80297</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2.445449</v>
+      </c>
+      <c r="E41" t="n">
+        <v>23.397422</v>
+      </c>
+      <c r="F41" t="n">
+        <v>56.263969</v>
+      </c>
+      <c r="G41" t="n">
+        <v>5.181771</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.53255</v>
+      </c>
+      <c r="I41" t="n">
+        <v>21.020488</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>163</v>
+      </c>
+      <c r="B42" t="n">
+        <v>7.290167</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.811087</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2.405727</v>
+      </c>
+      <c r="E42" t="n">
+        <v>22.416862</v>
+      </c>
+      <c r="F42" t="n">
+        <v>45.465898</v>
+      </c>
+      <c r="G42" t="n">
+        <v>3.545439</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.621443</v>
+      </c>
+      <c r="I42" t="n">
+        <v>29.874164</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>17</v>
+      </c>
+      <c r="B43" t="n">
+        <v>6.913886</v>
+      </c>
+      <c r="C43" t="n">
+        <v>31.422382</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2.363603</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.558547</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.297981</v>
+      </c>
+      <c r="G43" t="n">
+        <v>6.009281</v>
+      </c>
+      <c r="H43" t="n">
+        <v>3.234428</v>
+      </c>
+      <c r="I43" t="n">
+        <v>18.926279</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>149</v>
+      </c>
+      <c r="B44" t="n">
+        <v>6.50868</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1.033258</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2.316495</v>
+      </c>
+      <c r="E44" t="n">
+        <v>16.31563</v>
+      </c>
+      <c r="F44" t="n">
+        <v>45.207035</v>
+      </c>
+      <c r="G44" t="n">
+        <v>6.207954</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.705359</v>
+      </c>
+      <c r="I44" t="n">
+        <v>28.619333</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>18</v>
+      </c>
+      <c r="B45" t="n">
+        <v>6.329899</v>
+      </c>
+      <c r="C45" t="n">
+        <v>20.648795</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2.295088</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.801409</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.33502</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2.603773</v>
+      </c>
+      <c r="H45" t="n">
+        <v>2.313751</v>
+      </c>
+      <c r="I45" t="n">
+        <v>15.812325</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>155</v>
+      </c>
+      <c r="B46" t="n">
+        <v>5.838704</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1.045908</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2.234117</v>
+      </c>
+      <c r="E46" t="n">
+        <v>14.992296</v>
+      </c>
+      <c r="F46" t="n">
+        <v>42.410929</v>
+      </c>
+      <c r="G46" t="n">
+        <v>3.336185</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.561972</v>
+      </c>
+      <c r="I46" t="n">
+        <v>22.437291</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>169</v>
+      </c>
+      <c r="B47" t="n">
+        <v>5.18714</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.447637</v>
+      </c>
+      <c r="D47" t="n">
+        <v>2.147714</v>
+      </c>
+      <c r="E47" t="n">
+        <v>32.372507</v>
+      </c>
+      <c r="F47" t="n">
+        <v>100.010509</v>
+      </c>
+      <c r="G47" t="n">
+        <v>4.861887</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.380404</v>
+      </c>
+      <c r="I47" t="n">
+        <v>26.434907</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>19</v>
+      </c>
+      <c r="B48" t="n">
+        <v>5.013593</v>
+      </c>
+      <c r="C48" t="n">
+        <v>21.780192</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2.12349</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.650412</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.162109</v>
+      </c>
+      <c r="G48" t="n">
+        <v>2.859991</v>
+      </c>
+      <c r="H48" t="n">
+        <v>2.604195</v>
+      </c>
+      <c r="I48" t="n">
+        <v>23.280484</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>143</v>
+      </c>
+      <c r="B49" t="n">
+        <v>4.981144</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.764304</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2.118898</v>
+      </c>
+      <c r="E49" t="n">
+        <v>18.454575</v>
+      </c>
+      <c r="F49" t="n">
+        <v>26.361014</v>
+      </c>
+      <c r="G49" t="n">
+        <v>10.528924</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.758396</v>
+      </c>
+      <c r="I49" t="n">
+        <v>21.944436</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>22</v>
+      </c>
+      <c r="B50" t="n">
+        <v>4.964236</v>
+      </c>
+      <c r="C50" t="n">
+        <v>16.343281</v>
+      </c>
+      <c r="D50" t="n">
+        <v>2.116498</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.861086</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.486654</v>
+      </c>
+      <c r="G50" t="n">
+        <v>2.483968</v>
+      </c>
+      <c r="H50" t="n">
+        <v>2.182099</v>
+      </c>
+      <c r="I50" t="n">
+        <v>23.776225</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>177</v>
+      </c>
+      <c r="B51" t="n">
+        <v>4.877424</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.215336</v>
+      </c>
+      <c r="D51" t="n">
+        <v>2.104088</v>
+      </c>
+      <c r="E51" t="n">
+        <v>64.58942500000001</v>
+      </c>
+      <c r="F51" t="n">
+        <v>473.973742</v>
+      </c>
+      <c r="G51" t="n">
+        <v>9.767783</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.287457</v>
+      </c>
+      <c r="I51" t="n">
+        <v>28.217503</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>164</v>
+      </c>
+      <c r="B52" t="n">
+        <v>4.86602</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.569398</v>
+      </c>
+      <c r="D52" t="n">
+        <v>2.102447</v>
+      </c>
+      <c r="E52" t="n">
+        <v>24.38846</v>
+      </c>
+      <c r="F52" t="n">
+        <v>64.73889200000001</v>
+      </c>
+      <c r="G52" t="n">
+        <v>18.462205</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1.114264</v>
+      </c>
+      <c r="I52" t="n">
+        <v>21.466955</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>165</v>
+      </c>
+      <c r="B53" t="n">
+        <v>4.834043</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.641037</v>
+      </c>
+      <c r="D53" t="n">
+        <v>2.097832</v>
+      </c>
+      <c r="E53" t="n">
+        <v>21.5679</v>
+      </c>
+      <c r="F53" t="n">
+        <v>48.945381</v>
+      </c>
+      <c r="G53" t="n">
+        <v>2.468339</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.390113</v>
+      </c>
+      <c r="I53" t="n">
+        <v>23.499811</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>29</v>
+      </c>
+      <c r="B54" t="n">
+        <v>4.504623</v>
+      </c>
+      <c r="C54" t="n">
+        <v>17.182136</v>
+      </c>
+      <c r="D54" t="n">
+        <v>2.049053</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.767678</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.522772</v>
+      </c>
+      <c r="G54" t="n">
+        <v>5.504386</v>
+      </c>
+      <c r="H54" t="n">
+        <v>2.599099</v>
+      </c>
+      <c r="I54" t="n">
+        <v>23.020166</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>23</v>
+      </c>
+      <c r="B55" t="n">
+        <v>4.441579</v>
+      </c>
+      <c r="C55" t="n">
+        <v>14.874494</v>
+      </c>
+      <c r="D55" t="n">
+        <v>2.039449</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.878483</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.485318</v>
+      </c>
+      <c r="G55" t="n">
+        <v>2.519053</v>
+      </c>
+      <c r="H55" t="n">
+        <v>2.092366</v>
+      </c>
+      <c r="I55" t="n">
+        <v>18.325446</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>21</v>
+      </c>
+      <c r="B56" t="n">
+        <v>4.381483</v>
+      </c>
+      <c r="C56" t="n">
+        <v>18.04208</v>
+      </c>
+      <c r="D56" t="n">
+        <v>2.030209</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.717703</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.313318</v>
+      </c>
+      <c r="G56" t="n">
+        <v>2.552584</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1.929239</v>
+      </c>
+      <c r="I56" t="n">
+        <v>18.708247</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>24</v>
+      </c>
+      <c r="B57" t="n">
+        <v>4.201983</v>
+      </c>
+      <c r="C57" t="n">
+        <v>14.746091</v>
+      </c>
+      <c r="D57" t="n">
+        <v>2.002098</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.853972</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.479613</v>
+      </c>
+      <c r="G57" t="n">
+        <v>2.578449</v>
+      </c>
+      <c r="H57" t="n">
+        <v>2.144126</v>
+      </c>
+      <c r="I57" t="n">
+        <v>23.150813</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>25</v>
+      </c>
+      <c r="B58" t="n">
+        <v>4.13134</v>
+      </c>
+      <c r="C58" t="n">
+        <v>14.479235</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1.990814</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.859935</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.465278</v>
+      </c>
+      <c r="G58" t="n">
+        <v>2.423009</v>
+      </c>
+      <c r="H58" t="n">
+        <v>2.084659</v>
+      </c>
+      <c r="I58" t="n">
+        <v>26.185775</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>150</v>
+      </c>
+      <c r="B59" t="n">
+        <v>3.982766</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.933138</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1.966657</v>
+      </c>
+      <c r="E59" t="n">
+        <v>13.021511</v>
+      </c>
+      <c r="F59" t="n">
+        <v>22.188728</v>
+      </c>
+      <c r="G59" t="n">
+        <v>5.333664</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.786741</v>
+      </c>
+      <c r="I59" t="n">
+        <v>28.427784</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>140</v>
+      </c>
+      <c r="B60" t="n">
+        <v>3.368297</v>
+      </c>
+      <c r="C60" t="n">
+        <v>1.542343</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1.859819</v>
+      </c>
+      <c r="E60" t="n">
+        <v>7.045471</v>
+      </c>
+      <c r="F60" t="n">
+        <v>11.363152</v>
+      </c>
+      <c r="G60" t="n">
+        <v>2.282629</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.630637</v>
+      </c>
+      <c r="I60" t="n">
+        <v>22.323936</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>152</v>
+      </c>
+      <c r="B61" t="n">
+        <v>3.209339</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.833118</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1.83009</v>
+      </c>
+      <c r="E61" t="n">
+        <v>12.629557</v>
+      </c>
+      <c r="F61" t="n">
+        <v>15.232093</v>
+      </c>
+      <c r="G61" t="n">
+        <v>3.938045</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.566246</v>
+      </c>
+      <c r="I61" t="n">
+        <v>20.678606</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>20</v>
+      </c>
+      <c r="B62" t="n">
+        <v>3.052795</v>
+      </c>
+      <c r="C62" t="n">
+        <v>17.492881</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1.799836</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.581774</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.216436</v>
+      </c>
+      <c r="G62" t="n">
+        <v>2.006594</v>
+      </c>
+      <c r="H62" t="n">
+        <v>1.824972</v>
+      </c>
+      <c r="I62" t="n">
+        <v>26.157016</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>27</v>
+      </c>
+      <c r="B63" t="n">
+        <v>2.982801</v>
+      </c>
+      <c r="C63" t="n">
+        <v>11.444315</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1.785974</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.87561</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.466438</v>
+      </c>
+      <c r="G63" t="n">
+        <v>2.416516</v>
+      </c>
+      <c r="H63" t="n">
+        <v>1.792032</v>
+      </c>
+      <c r="I63" t="n">
+        <v>20.864247</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>172</v>
+      </c>
+      <c r="B64" t="n">
+        <v>2.948078</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.185349</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1.779017</v>
+      </c>
+      <c r="E64" t="n">
+        <v>53.643853</v>
+      </c>
+      <c r="F64" t="n">
+        <v>208.019415</v>
+      </c>
+      <c r="G64" t="n">
+        <v>23.734017</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="I64" t="n">
+        <v>25.24717</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>32</v>
+      </c>
+      <c r="B65" t="n">
+        <v>2.814226</v>
+      </c>
+      <c r="C65" t="n">
+        <v>10.936011</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1.751675</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.88145</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.489791</v>
+      </c>
+      <c r="G65" t="n">
+        <v>2.608673</v>
+      </c>
+      <c r="H65" t="n">
+        <v>1.832685</v>
+      </c>
+      <c r="I65" t="n">
+        <v>22.934508</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>28</v>
+      </c>
+      <c r="B66" t="n">
+        <v>2.776403</v>
+      </c>
+      <c r="C66" t="n">
+        <v>11.183947</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1.743792</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.85417</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.353282</v>
+      </c>
+      <c r="G66" t="n">
+        <v>2.376327</v>
+      </c>
+      <c r="H66" t="n">
+        <v>1.709123</v>
+      </c>
+      <c r="I66" t="n">
+        <v>25.181533</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>30</v>
+      </c>
+      <c r="B67" t="n">
+        <v>2.697292</v>
+      </c>
+      <c r="C67" t="n">
+        <v>10.932606</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1.727069</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.857128</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.429034</v>
+      </c>
+      <c r="G67" t="n">
+        <v>2.556736</v>
+      </c>
+      <c r="H67" t="n">
+        <v>1.819812</v>
+      </c>
+      <c r="I67" t="n">
+        <v>24.869538</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>33</v>
+      </c>
+      <c r="B68" t="n">
+        <v>2.622731</v>
+      </c>
+      <c r="C68" t="n">
+        <v>10.588476</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1.711007</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.8686</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.487889</v>
+      </c>
+      <c r="G68" t="n">
+        <v>2.467615</v>
+      </c>
+      <c r="H68" t="n">
+        <v>1.741384</v>
+      </c>
+      <c r="I68" t="n">
+        <v>10.724325</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>161</v>
+      </c>
+      <c r="B69" t="n">
+        <v>2.611441</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0.75146</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1.708548</v>
+      </c>
+      <c r="E69" t="n">
+        <v>12.203887</v>
+      </c>
+      <c r="F69" t="n">
+        <v>26.767014</v>
+      </c>
+      <c r="G69" t="n">
+        <v>3.432038</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.535646</v>
+      </c>
+      <c r="I69" t="n">
+        <v>25.139464</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>123</v>
+      </c>
+      <c r="B70" t="n">
+        <v>2.51087</v>
+      </c>
+      <c r="C70" t="n">
+        <v>1.132682</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1.686327</v>
+      </c>
+      <c r="E70" t="n">
+        <v>7.887251</v>
+      </c>
+      <c r="F70" t="n">
+        <v>8.001396</v>
+      </c>
+      <c r="G70" t="n">
+        <v>10.692074</v>
+      </c>
+      <c r="H70" t="n">
+        <v>1.189179</v>
+      </c>
+      <c r="I70" t="n">
+        <v>25.822374</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>40</v>
+      </c>
+      <c r="B71" t="n">
+        <v>2.378624</v>
+      </c>
+      <c r="C71" t="n">
+        <v>10.5809</v>
+      </c>
+      <c r="D71" t="n">
+        <v>1.656186</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.814414</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.248545</v>
+      </c>
+      <c r="G71" t="n">
+        <v>1.952177</v>
+      </c>
+      <c r="H71" t="n">
+        <v>1.529055</v>
+      </c>
+      <c r="I71" t="n">
+        <v>26.24968</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>36</v>
+      </c>
+      <c r="B72" t="n">
+        <v>2.243595</v>
+      </c>
+      <c r="C72" t="n">
+        <v>9.517996</v>
+      </c>
+      <c r="D72" t="n">
+        <v>1.624234</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.870766</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.434005</v>
+      </c>
+      <c r="G72" t="n">
+        <v>2.447763</v>
+      </c>
+      <c r="H72" t="n">
+        <v>1.645194</v>
+      </c>
+      <c r="I72" t="n">
+        <v>18.297971</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>134</v>
+      </c>
+      <c r="B73" t="n">
+        <v>2.235421</v>
+      </c>
+      <c r="C73" t="n">
+        <v>1.818715</v>
+      </c>
+      <c r="D73" t="n">
+        <v>1.622259</v>
+      </c>
+      <c r="E73" t="n">
+        <v>4.545962</v>
+      </c>
+      <c r="F73" t="n">
+        <v>4.73579</v>
+      </c>
+      <c r="G73" t="n">
+        <v>4.221298</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.84095</v>
+      </c>
+      <c r="I73" t="n">
+        <v>25.911688</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>162</v>
+      </c>
+      <c r="B74" t="n">
+        <v>2.196182</v>
+      </c>
+      <c r="C74" t="n">
+        <v>0.432314</v>
+      </c>
+      <c r="D74" t="n">
+        <v>1.612711</v>
+      </c>
+      <c r="E74" t="n">
+        <v>18.900078</v>
+      </c>
+      <c r="F74" t="n">
+        <v>30.719791</v>
+      </c>
+      <c r="G74" t="n">
+        <v>7.03197</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.688891</v>
+      </c>
+      <c r="I74" t="n">
+        <v>21.047174</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>35</v>
+      </c>
+      <c r="B75" t="n">
+        <v>2.169734</v>
+      </c>
+      <c r="C75" t="n">
+        <v>11.064941</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1.606211</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.732497</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.319986</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1.13647</v>
+      </c>
+      <c r="H75" t="n">
+        <v>1.169674</v>
+      </c>
+      <c r="I75" t="n">
+        <v>28.142964</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>176</v>
+      </c>
+      <c r="B76" t="n">
+        <v>2.124329</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0.226902</v>
+      </c>
+      <c r="D76" t="n">
+        <v>1.594928</v>
+      </c>
+      <c r="E76" t="n">
+        <v>35.220414</v>
+      </c>
+      <c r="F76" t="n">
+        <v>47.377164</v>
+      </c>
+      <c r="G76" t="n">
+        <v>4.188476</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.394224</v>
+      </c>
+      <c r="I76" t="n">
+        <v>27.273941</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>38</v>
+      </c>
+      <c r="B77" t="n">
+        <v>2.120231</v>
+      </c>
+      <c r="C77" t="n">
+        <v>9.401101000000001</v>
+      </c>
+      <c r="D77" t="n">
+        <v>1.593902</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.848974</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.46406</v>
+      </c>
+      <c r="G77" t="n">
+        <v>2.75204</v>
+      </c>
+      <c r="H77" t="n">
+        <v>1.718449</v>
+      </c>
+      <c r="I77" t="n">
+        <v>19.421016</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>167</v>
+      </c>
+      <c r="B78" t="n">
+        <v>2.093666</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0.505077</v>
+      </c>
+      <c r="D78" t="n">
+        <v>1.587217</v>
+      </c>
+      <c r="E78" t="n">
+        <v>15.669843</v>
+      </c>
+      <c r="F78" t="n">
+        <v>31.762926</v>
+      </c>
+      <c r="G78" t="n">
+        <v>1.650627</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.301351</v>
+      </c>
+      <c r="I78" t="n">
+        <v>22.655109</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>41</v>
+      </c>
+      <c r="B79" t="n">
+        <v>2.076703</v>
+      </c>
+      <c r="C79" t="n">
+        <v>9.287407</v>
+      </c>
+      <c r="D79" t="n">
+        <v>1.582919</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.847564</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.441931</v>
+      </c>
+      <c r="G79" t="n">
+        <v>2.342618</v>
+      </c>
+      <c r="H79" t="n">
+        <v>1.583374</v>
+      </c>
+      <c r="I79" t="n">
+        <v>26.977172</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>43</v>
+      </c>
+      <c r="B80" t="n">
+        <v>1.940883</v>
+      </c>
+      <c r="C80" t="n">
+        <v>8.597395000000001</v>
+      </c>
+      <c r="D80" t="n">
+        <v>1.547629</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.875219</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.484624</v>
+      </c>
+      <c r="G80" t="n">
+        <v>2.342816</v>
+      </c>
+      <c r="H80" t="n">
+        <v>1.544601</v>
+      </c>
+      <c r="I80" t="n">
+        <v>19.492773</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>85</v>
+      </c>
+      <c r="B81" t="n">
+        <v>1.844868</v>
+      </c>
+      <c r="C81" t="n">
+        <v>4.950453</v>
+      </c>
+      <c r="D81" t="n">
+        <v>1.521676</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1.469432</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1.009631</v>
+      </c>
+      <c r="G81" t="n">
+        <v>2.458127</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.990791</v>
+      </c>
+      <c r="I81" t="n">
+        <v>25.514032</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>175</v>
+      </c>
+      <c r="B82" t="n">
+        <v>1.788264</v>
+      </c>
+      <c r="C82" t="n">
+        <v>0.196346</v>
+      </c>
+      <c r="D82" t="n">
+        <v>1.505951</v>
+      </c>
+      <c r="E82" t="n">
+        <v>36.28698</v>
+      </c>
+      <c r="F82" t="n">
+        <v>174.75463</v>
+      </c>
+      <c r="G82" t="n">
+        <v>3.999269</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0.275329</v>
+      </c>
+      <c r="I82" t="n">
+        <v>19.996654</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>44</v>
+      </c>
+      <c r="B83" t="n">
+        <v>1.785866</v>
+      </c>
+      <c r="C83" t="n">
+        <v>11.272267</v>
+      </c>
+      <c r="D83" t="n">
+        <v>1.505278</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.631498</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.39723</v>
+      </c>
+      <c r="G83" t="n">
+        <v>6.330251</v>
+      </c>
+      <c r="H83" t="n">
+        <v>2.274192</v>
+      </c>
+      <c r="I83" t="n">
+        <v>16.582259</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>141</v>
+      </c>
+      <c r="B84" t="n">
+        <v>1.780427</v>
+      </c>
+      <c r="C84" t="n">
+        <v>1.240863</v>
+      </c>
+      <c r="D84" t="n">
+        <v>1.503748</v>
+      </c>
+      <c r="E84" t="n">
+        <v>5.725013</v>
+      </c>
+      <c r="F84" t="n">
+        <v>9.292956</v>
+      </c>
+      <c r="G84" t="n">
+        <v>2.069317</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0.565156</v>
+      </c>
+      <c r="I84" t="n">
+        <v>26.073334</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>66</v>
+      </c>
+      <c r="B85" t="n">
+        <v>1.745793</v>
+      </c>
+      <c r="C85" t="n">
+        <v>4.689298</v>
+      </c>
+      <c r="D85" t="n">
+        <v>1.493934</v>
+      </c>
+      <c r="E85" t="n">
+        <v>1.495219</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0.846392</v>
+      </c>
+      <c r="G85" t="n">
+        <v>4.100812</v>
+      </c>
+      <c r="H85" t="n">
+        <v>1.52277</v>
+      </c>
+      <c r="I85" t="n">
+        <v>19.621818</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>184</v>
+      </c>
+      <c r="B86" t="n">
+        <v>1.657281</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0.054736</v>
+      </c>
+      <c r="D86" t="n">
+        <v>1.468247</v>
+      </c>
+      <c r="E86" t="n">
+        <v>123.728935</v>
+      </c>
+      <c r="F86" t="n">
+        <v>561788.064807</v>
+      </c>
+      <c r="G86" t="n">
+        <v>5037.668948</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0.15258</v>
+      </c>
+      <c r="I86" t="n">
+        <v>26.935632</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>52</v>
+      </c>
+      <c r="B87" t="n">
+        <v>1.616383</v>
+      </c>
+      <c r="C87" t="n">
+        <v>8.730275000000001</v>
+      </c>
+      <c r="D87" t="n">
+        <v>1.456069</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.7629320000000001</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.290093</v>
+      </c>
+      <c r="G87" t="n">
+        <v>2.159713</v>
+      </c>
+      <c r="H87" t="n">
+        <v>1.468736</v>
+      </c>
+      <c r="I87" t="n">
+        <v>27.374069</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>48</v>
+      </c>
+      <c r="B88" t="n">
+        <v>1.609678</v>
+      </c>
+      <c r="C88" t="n">
+        <v>7.754959</v>
+      </c>
+      <c r="D88" t="n">
+        <v>1.454053</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.856506</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0.440795</v>
+      </c>
+      <c r="G88" t="n">
+        <v>2.505855</v>
+      </c>
+      <c r="H88" t="n">
+        <v>1.547395</v>
+      </c>
+      <c r="I88" t="n">
+        <v>23.059592</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>120</v>
+      </c>
+      <c r="B89" t="n">
+        <v>1.606079</v>
+      </c>
+      <c r="C89" t="n">
+        <v>2.8023</v>
+      </c>
+      <c r="D89" t="n">
+        <v>1.452968</v>
+      </c>
+      <c r="E89" t="n">
+        <v>2.366724</v>
+      </c>
+      <c r="F89" t="n">
+        <v>2.027988</v>
+      </c>
+      <c r="G89" t="n">
+        <v>2.136618</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0.687232</v>
+      </c>
+      <c r="I89" t="n">
+        <v>24.505591</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>47</v>
+      </c>
+      <c r="B90" t="n">
+        <v>1.571907</v>
+      </c>
+      <c r="C90" t="n">
+        <v>7.620038</v>
+      </c>
+      <c r="D90" t="n">
+        <v>1.442589</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.857982</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0.451925</v>
+      </c>
+      <c r="G90" t="n">
+        <v>2.553087</v>
+      </c>
+      <c r="H90" t="n">
+        <v>1.51751</v>
+      </c>
+      <c r="I90" t="n">
+        <v>22.351482</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>74</v>
+      </c>
+      <c r="B91" t="n">
+        <v>1.569339</v>
+      </c>
+      <c r="C91" t="n">
+        <v>6.017668</v>
+      </c>
+      <c r="D91" t="n">
+        <v>1.441803</v>
+      </c>
+      <c r="E91" t="n">
+        <v>1.08526</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0.851522</v>
+      </c>
+      <c r="G91" t="n">
+        <v>2.82511</v>
+      </c>
+      <c r="H91" t="n">
+        <v>1.063025</v>
+      </c>
+      <c r="I91" t="n">
+        <v>25.238536</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>173</v>
+      </c>
+      <c r="B92" t="n">
+        <v>1.562031</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0.238775</v>
+      </c>
+      <c r="D92" t="n">
+        <v>1.439562</v>
+      </c>
+      <c r="E92" t="n">
+        <v>27.266026</v>
+      </c>
+      <c r="F92" t="n">
+        <v>45.263409</v>
+      </c>
+      <c r="G92" t="n">
+        <v>5.851192</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0.331521</v>
+      </c>
+      <c r="I92" t="n">
+        <v>24.351948</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>55</v>
+      </c>
+      <c r="B93" t="n">
+        <v>1.54196</v>
+      </c>
+      <c r="C93" t="n">
+        <v>7.23702</v>
+      </c>
+      <c r="D93" t="n">
+        <v>1.433369</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.89188</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0.492611</v>
+      </c>
+      <c r="G93" t="n">
+        <v>2.113987</v>
+      </c>
+      <c r="H93" t="n">
+        <v>1.351859</v>
+      </c>
+      <c r="I93" t="n">
+        <v>16.896184</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>50</v>
+      </c>
+      <c r="B94" t="n">
+        <v>1.474398</v>
+      </c>
+      <c r="C94" t="n">
+        <v>7.22989</v>
+      </c>
+      <c r="D94" t="n">
+        <v>1.412121</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.866488</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0.457352</v>
+      </c>
+      <c r="G94" t="n">
+        <v>2.509339</v>
+      </c>
+      <c r="H94" t="n">
+        <v>1.463316</v>
+      </c>
+      <c r="I94" t="n">
+        <v>17.969064</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>49</v>
+      </c>
+      <c r="B95" t="n">
+        <v>1.401757</v>
+      </c>
+      <c r="C95" t="n">
+        <v>7.367028</v>
+      </c>
+      <c r="D95" t="n">
+        <v>1.388539</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0.822193</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0.42279</v>
+      </c>
+      <c r="G95" t="n">
+        <v>2.761528</v>
+      </c>
+      <c r="H95" t="n">
+        <v>1.594174</v>
+      </c>
+      <c r="I95" t="n">
+        <v>24.479971</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>46</v>
+      </c>
+      <c r="B96" t="n">
+        <v>1.394096</v>
+      </c>
+      <c r="C96" t="n">
+        <v>7.742134</v>
+      </c>
+      <c r="D96" t="n">
+        <v>1.386005</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.779504</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="G96" t="n">
+        <v>2.410422</v>
+      </c>
+      <c r="H96" t="n">
+        <v>1.165966</v>
+      </c>
+      <c r="I96" t="n">
+        <v>22.741603</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>171</v>
+      </c>
+      <c r="B97" t="n">
+        <v>1.38222</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0.368469</v>
+      </c>
+      <c r="D97" t="n">
+        <v>1.382058</v>
+      </c>
+      <c r="E97" t="n">
+        <v>16.28551</v>
+      </c>
+      <c r="F97" t="n">
+        <v>37.382059</v>
+      </c>
+      <c r="G97" t="n">
+        <v>3.304307</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0.386894</v>
+      </c>
+      <c r="I97" t="n">
+        <v>21.056016</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>57</v>
+      </c>
+      <c r="B98" t="n">
+        <v>1.330447</v>
+      </c>
+      <c r="C98" t="n">
+        <v>6.637785</v>
+      </c>
+      <c r="D98" t="n">
+        <v>1.364582</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.881304</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0.451092</v>
+      </c>
+      <c r="G98" t="n">
+        <v>2.404406</v>
+      </c>
+      <c r="H98" t="n">
+        <v>1.354684</v>
+      </c>
+      <c r="I98" t="n">
+        <v>15.592791</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>53</v>
+      </c>
+      <c r="B99" t="n">
+        <v>1.321575</v>
+      </c>
+      <c r="C99" t="n">
+        <v>6.907501</v>
+      </c>
+      <c r="D99" t="n">
+        <v>1.361542</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0.843123</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0.411507</v>
+      </c>
+      <c r="G99" t="n">
+        <v>2.583055</v>
+      </c>
+      <c r="H99" t="n">
+        <v>1.486088</v>
+      </c>
+      <c r="I99" t="n">
+        <v>17.648947</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>67</v>
+      </c>
+      <c r="B100" t="n">
+        <v>1.289247</v>
+      </c>
+      <c r="C100" t="n">
+        <v>7.589264</v>
+      </c>
+      <c r="D100" t="n">
+        <v>1.350348</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.754817</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0.496636</v>
+      </c>
+      <c r="G100" t="n">
+        <v>4.689683</v>
+      </c>
+      <c r="H100" t="n">
+        <v>1.621078</v>
+      </c>
+      <c r="I100" t="n">
+        <v>27.476683</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>56</v>
+      </c>
+      <c r="B101" t="n">
+        <v>1.272756</v>
+      </c>
+      <c r="C101" t="n">
+        <v>6.924522</v>
+      </c>
+      <c r="D101" t="n">
+        <v>1.344566</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.820209</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0.453902</v>
+      </c>
+      <c r="G101" t="n">
+        <v>3.123693</v>
+      </c>
+      <c r="H101" t="n">
+        <v>1.521673</v>
+      </c>
+      <c r="I101" t="n">
+        <v>14.214794</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>42</v>
+      </c>
+      <c r="B102" t="n">
+        <v>1.244438</v>
+      </c>
+      <c r="C102" t="n">
+        <v>8.139486</v>
+      </c>
+      <c r="D102" t="n">
+        <v>1.334519</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0.687389</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0.272054</v>
+      </c>
+      <c r="G102" t="n">
+        <v>3.282345</v>
+      </c>
+      <c r="H102" t="n">
+        <v>1.404563</v>
+      </c>
+      <c r="I102" t="n">
+        <v>13.032583</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>60</v>
+      </c>
+      <c r="B103" t="n">
+        <v>1.181876</v>
+      </c>
+      <c r="C103" t="n">
+        <v>6.001862</v>
+      </c>
+      <c r="D103" t="n">
+        <v>1.31177</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0.900698</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0.49013</v>
+      </c>
+      <c r="G103" t="n">
+        <v>2.151321</v>
+      </c>
+      <c r="H103" t="n">
+        <v>1.213506</v>
+      </c>
+      <c r="I103" t="n">
+        <v>26.195355</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>51</v>
+      </c>
+      <c r="B104" t="n">
+        <v>1.067159</v>
+      </c>
+      <c r="C104" t="n">
+        <v>6.933856</v>
+      </c>
+      <c r="D104" t="n">
+        <v>1.267876</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0.728331</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0.184277</v>
+      </c>
+      <c r="G104" t="n">
+        <v>3.828876</v>
+      </c>
+      <c r="H104" t="n">
+        <v>1.750641</v>
+      </c>
+      <c r="I104" t="n">
+        <v>22.365804</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>182</v>
+      </c>
+      <c r="B105" t="n">
+        <v>1.034566</v>
+      </c>
+      <c r="C105" t="n">
+        <v>0.113061</v>
+      </c>
+      <c r="D105" t="n">
+        <v>1.254835</v>
+      </c>
+      <c r="E105" t="n">
+        <v>43.753395</v>
+      </c>
+      <c r="F105" t="n">
+        <v>46.117926</v>
+      </c>
+      <c r="G105" t="n">
+        <v>4.447391</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0.301907</v>
+      </c>
+      <c r="I105" t="n">
+        <v>21.674393</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>64</v>
+      </c>
+      <c r="B106" t="n">
+        <v>1.026372</v>
+      </c>
+      <c r="C106" t="n">
+        <v>5.489203</v>
+      </c>
+      <c r="D106" t="n">
+        <v>1.251513</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0.89642</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0.471371</v>
+      </c>
+      <c r="G106" t="n">
+        <v>2.195171</v>
+      </c>
+      <c r="H106" t="n">
+        <v>1.175531</v>
+      </c>
+      <c r="I106" t="n">
+        <v>22.6699</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>185</v>
+      </c>
+      <c r="B107" t="n">
+        <v>1.018964</v>
+      </c>
+      <c r="C107" t="n">
+        <v>0.033647</v>
+      </c>
+      <c r="D107" t="n">
+        <v>1.248495</v>
+      </c>
+      <c r="E107" t="n">
+        <v>145.536121</v>
+      </c>
+      <c r="F107" t="n">
+        <v>489564.08392</v>
+      </c>
+      <c r="G107" t="n">
+        <v>6937.787521</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0.197236</v>
+      </c>
+      <c r="I107" t="n">
+        <v>25.240964</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>63</v>
+      </c>
+      <c r="B108" t="n">
+        <v>1.010643</v>
+      </c>
+      <c r="C108" t="n">
+        <v>5.502699</v>
+      </c>
+      <c r="D108" t="n">
+        <v>1.245087</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0.885062</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0.473957</v>
+      </c>
+      <c r="G108" t="n">
+        <v>2.231356</v>
+      </c>
+      <c r="H108" t="n">
+        <v>1.209523</v>
+      </c>
+      <c r="I108" t="n">
+        <v>6.711779</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>178</v>
+      </c>
+      <c r="B109" t="n">
+        <v>1.00174</v>
+      </c>
+      <c r="C109" t="n">
+        <v>0.168116</v>
+      </c>
+      <c r="D109" t="n">
+        <v>1.24142</v>
+      </c>
+      <c r="E109" t="n">
+        <v>28.799137</v>
+      </c>
+      <c r="F109" t="n">
+        <v>80.008178</v>
+      </c>
+      <c r="G109" t="n">
+        <v>3.722948</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0.248563</v>
+      </c>
+      <c r="I109" t="n">
+        <v>23.323199</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>61</v>
+      </c>
+      <c r="B110" t="n">
+        <v>0.99496</v>
+      </c>
+      <c r="C110" t="n">
+        <v>5.546605</v>
+      </c>
+      <c r="D110" t="n">
+        <v>1.238613</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0.8689480000000001</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0.419799</v>
+      </c>
+      <c r="G110" t="n">
+        <v>2.408307</v>
+      </c>
+      <c r="H110" t="n">
+        <v>1.267086</v>
+      </c>
+      <c r="I110" t="n">
+        <v>23.675066</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>62</v>
+      </c>
+      <c r="B111" t="n">
+        <v>0.937131</v>
+      </c>
+      <c r="C111" t="n">
+        <v>5.491275</v>
+      </c>
+      <c r="D111" t="n">
+        <v>1.214136</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0.843356</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0.312885</v>
+      </c>
+      <c r="G111" t="n">
+        <v>1.953154</v>
+      </c>
+      <c r="H111" t="n">
+        <v>1.070254</v>
+      </c>
+      <c r="I111" t="n">
+        <v>23.557882</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>174</v>
+      </c>
+      <c r="B112" t="n">
+        <v>0.907591</v>
+      </c>
+      <c r="C112" t="n">
+        <v>0.315211</v>
+      </c>
+      <c r="D112" t="n">
+        <v>1.201242</v>
+      </c>
+      <c r="E112" t="n">
+        <v>14.381689</v>
+      </c>
+      <c r="F112" t="n">
+        <v>18.982541</v>
+      </c>
+      <c r="G112" t="n">
+        <v>10.148336</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0.528397</v>
+      </c>
+      <c r="I112" t="n">
+        <v>21.087106</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>168</v>
+      </c>
+      <c r="B113" t="n">
+        <v>0.8755849999999999</v>
+      </c>
+      <c r="C113" t="n">
+        <v>0.429215</v>
+      </c>
+      <c r="D113" t="n">
+        <v>1.186952</v>
+      </c>
+      <c r="E113" t="n">
+        <v>10.311957</v>
+      </c>
+      <c r="F113" t="n">
+        <v>14.220152</v>
+      </c>
+      <c r="G113" t="n">
+        <v>2.956008</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0.378637</v>
+      </c>
+      <c r="I113" t="n">
+        <v>20.672077</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>72</v>
+      </c>
+      <c r="B114" t="n">
+        <v>0.818148</v>
+      </c>
+      <c r="C114" t="n">
+        <v>4.778723</v>
+      </c>
+      <c r="D114" t="n">
+        <v>1.160409</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0.885238</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0.5248930000000001</v>
+      </c>
+      <c r="G114" t="n">
+        <v>2.405194</v>
+      </c>
+      <c r="H114" t="n">
+        <v>1.153528</v>
+      </c>
+      <c r="I114" t="n">
+        <v>20.32256</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>80</v>
+      </c>
+      <c r="B115" t="n">
+        <v>0.789263</v>
+      </c>
+      <c r="C115" t="n">
+        <v>4.315181</v>
+      </c>
+      <c r="D115" t="n">
+        <v>1.146589</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0.95712</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0.6543060000000001</v>
+      </c>
+      <c r="G115" t="n">
+        <v>2.815282</v>
+      </c>
+      <c r="H115" t="n">
+        <v>1.089752</v>
+      </c>
+      <c r="I115" t="n">
+        <v>22.221439</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>180</v>
+      </c>
+      <c r="B116" t="n">
+        <v>0.779549</v>
+      </c>
+      <c r="C116" t="n">
+        <v>0.096168</v>
+      </c>
+      <c r="D116" t="n">
+        <v>1.141865</v>
+      </c>
+      <c r="E116" t="n">
+        <v>42.59392</v>
+      </c>
+      <c r="F116" t="n">
+        <v>273.659262</v>
+      </c>
+      <c r="G116" t="n">
+        <v>6.850559</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0.187761</v>
+      </c>
+      <c r="I116" t="n">
+        <v>17.546862</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>65</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.7775609999999999</v>
+      </c>
+      <c r="C117" t="n">
+        <v>5.138256</v>
+      </c>
+      <c r="D117" t="n">
+        <v>1.140894</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.795838</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.345206</v>
+      </c>
+      <c r="G117" t="n">
+        <v>2.915789</v>
+      </c>
+      <c r="H117" t="n">
+        <v>1.323689</v>
+      </c>
+      <c r="I117" t="n">
+        <v>25.171877</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>142</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.745044</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1.303243</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.124763</v>
+      </c>
+      <c r="E118" t="n">
+        <v>3.049626</v>
+      </c>
+      <c r="F118" t="n">
+        <v>3.15911</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.969807</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.543606</v>
+      </c>
+      <c r="I118" t="n">
+        <v>26.084248</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>153</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.705189</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.683745</v>
+      </c>
+      <c r="D119" t="n">
+        <v>1.104338</v>
+      </c>
+      <c r="E119" t="n">
+        <v>5.603508</v>
+      </c>
+      <c r="F119" t="n">
+        <v>4.960326</v>
+      </c>
+      <c r="G119" t="n">
+        <v>8.696095</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.799427</v>
+      </c>
+      <c r="I119" t="n">
+        <v>25.729877</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>73</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.69656</v>
+      </c>
+      <c r="C120" t="n">
+        <v>4.309279</v>
+      </c>
+      <c r="D120" t="n">
+        <v>1.099816</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.881831</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.430077</v>
+      </c>
+      <c r="G120" t="n">
+        <v>2.002469</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.96721</v>
+      </c>
+      <c r="I120" t="n">
+        <v>12.539378</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>76</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.691634</v>
+      </c>
+      <c r="C121" t="n">
+        <v>5.147902</v>
+      </c>
+      <c r="D121" t="n">
+        <v>1.097217</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.734691</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.394011</v>
+      </c>
+      <c r="G121" t="n">
+        <v>4.23659</v>
+      </c>
+      <c r="H121" t="n">
+        <v>1.410029</v>
+      </c>
+      <c r="I121" t="n">
+        <v>29.32315</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>71</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.671691</v>
+      </c>
+      <c r="C122" t="n">
+        <v>4.452746</v>
+      </c>
+      <c r="D122" t="n">
+        <v>1.086568</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.832983</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.426153</v>
+      </c>
+      <c r="G122" t="n">
+        <v>2.696663</v>
+      </c>
+      <c r="H122" t="n">
+        <v>1.202895</v>
+      </c>
+      <c r="I122" t="n">
+        <v>18.535676</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>159</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.651201</v>
+      </c>
+      <c r="C123" t="n">
+        <v>0.454633</v>
+      </c>
+      <c r="D123" t="n">
+        <v>1.075405</v>
+      </c>
+      <c r="E123" t="n">
+        <v>7.991592</v>
+      </c>
+      <c r="F123" t="n">
+        <v>5.569309</v>
+      </c>
+      <c r="G123" t="n">
+        <v>12.103421</v>
+      </c>
+      <c r="H123" t="n">
+        <v>1.045659</v>
+      </c>
+      <c r="I123" t="n">
+        <v>20.895409</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>75</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.640142</v>
+      </c>
+      <c r="C124" t="n">
+        <v>4.028516</v>
+      </c>
+      <c r="D124" t="n">
+        <v>1.069283</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0.891641</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.490785</v>
+      </c>
+      <c r="G124" t="n">
+        <v>2.319811</v>
+      </c>
+      <c r="H124" t="n">
+        <v>1.025024</v>
+      </c>
+      <c r="I124" t="n">
+        <v>16.609166</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>58</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.631637</v>
+      </c>
+      <c r="C125" t="n">
+        <v>6.252596</v>
+      </c>
+      <c r="D125" t="n">
+        <v>1.064526</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.56938</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.225382</v>
+      </c>
+      <c r="G125" t="n">
+        <v>2.583226</v>
+      </c>
+      <c r="H125" t="n">
+        <v>1.405626</v>
+      </c>
+      <c r="I125" t="n">
+        <v>15.84758</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>70</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.622907</v>
+      </c>
+      <c r="C126" t="n">
+        <v>4.702442</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.059599</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0.7500830000000001</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.299945</v>
+      </c>
+      <c r="G126" t="n">
+        <v>2.800708</v>
+      </c>
+      <c r="H126" t="n">
+        <v>1.04978</v>
+      </c>
+      <c r="I126" t="n">
+        <v>24.106688</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>77</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.606892</v>
+      </c>
+      <c r="C127" t="n">
+        <v>3.855268</v>
+      </c>
+      <c r="D127" t="n">
+        <v>1.050439</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.89916</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.48925</v>
+      </c>
+      <c r="G127" t="n">
+        <v>2.175526</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.976326</v>
+      </c>
+      <c r="I127" t="n">
+        <v>19.426989</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>54</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.6068170000000001</v>
+      </c>
+      <c r="C128" t="n">
+        <v>5.807214</v>
+      </c>
+      <c r="D128" t="n">
+        <v>1.050396</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.596882</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.20124</v>
+      </c>
+      <c r="G128" t="n">
+        <v>3.854279</v>
+      </c>
+      <c r="H128" t="n">
+        <v>1.346034</v>
+      </c>
+      <c r="I128" t="n">
+        <v>25.475722</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>181</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.604955</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.052346</v>
+      </c>
+      <c r="D129" t="n">
+        <v>1.04932</v>
+      </c>
+      <c r="E129" t="n">
+        <v>66.081514</v>
+      </c>
+      <c r="F129" t="n">
+        <v>236.703323</v>
+      </c>
+      <c r="G129" t="n">
+        <v>10.363754</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.222917</v>
+      </c>
+      <c r="I129" t="n">
+        <v>24.537848</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>59</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.598085</v>
+      </c>
+      <c r="C130" t="n">
+        <v>5.952573</v>
+      </c>
+      <c r="D130" t="n">
+        <v>1.045333</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.5767060000000001</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.170122</v>
+      </c>
+      <c r="G130" t="n">
+        <v>2.216156</v>
+      </c>
+      <c r="H130" t="n">
+        <v>1.185556</v>
+      </c>
+      <c r="I130" t="n">
+        <v>28.016388</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>79</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.573723</v>
+      </c>
+      <c r="C131" t="n">
+        <v>3.722475</v>
+      </c>
+      <c r="D131" t="n">
+        <v>1.030943</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.896989</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.516606</v>
+      </c>
+      <c r="G131" t="n">
+        <v>2.255566</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.987434</v>
+      </c>
+      <c r="I131" t="n">
+        <v>16.84915</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>86</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.507857</v>
+      </c>
+      <c r="C132" t="n">
+        <v>3.424541</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.989876</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.898896</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.516637</v>
+      </c>
+      <c r="G132" t="n">
+        <v>2.300209</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.9273</v>
+      </c>
+      <c r="I132" t="n">
+        <v>17.440882</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>144</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.49207</v>
+      </c>
+      <c r="C133" t="n">
+        <v>1.546182</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.979511</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1.949433</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.434953</v>
+      </c>
+      <c r="G133" t="n">
+        <v>1.780621</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.507471</v>
+      </c>
+      <c r="I133" t="n">
+        <v>26.965784</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>82</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.483686</v>
+      </c>
+      <c r="C134" t="n">
+        <v>3.44528</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.973916</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.864905</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.382456</v>
+      </c>
+      <c r="G134" t="n">
+        <v>2.099434</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.931003</v>
+      </c>
+      <c r="I134" t="n">
+        <v>14.903051</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>83</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.479421</v>
+      </c>
+      <c r="C135" t="n">
+        <v>3.350555</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.971045</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.884122</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.422248</v>
+      </c>
+      <c r="G135" t="n">
+        <v>2.360295</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.936253</v>
+      </c>
+      <c r="I135" t="n">
+        <v>15.910259</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>87</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.478151</v>
+      </c>
+      <c r="C136" t="n">
+        <v>3.237698</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.970187</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.913323</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.504823</v>
+      </c>
+      <c r="G136" t="n">
+        <v>1.93098</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.8735619999999999</v>
+      </c>
+      <c r="I136" t="n">
+        <v>20.963595</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>81</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.476995</v>
+      </c>
+      <c r="C137" t="n">
+        <v>3.418799</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.969405</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.863548</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.544505</v>
+      </c>
+      <c r="G137" t="n">
+        <v>2.26638</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.976464</v>
+      </c>
+      <c r="I137" t="n">
+        <v>12.068362</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>91</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.452554</v>
+      </c>
+      <c r="C138" t="n">
+        <v>3.108241</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.952556</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.917099</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.562215</v>
+      </c>
+      <c r="G138" t="n">
+        <v>1.958914</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.839942</v>
+      </c>
+      <c r="I138" t="n">
+        <v>23.819682</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>93</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.446472</v>
+      </c>
+      <c r="C139" t="n">
+        <v>2.96191</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.9482699999999999</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.953766</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.575574</v>
+      </c>
+      <c r="G139" t="n">
+        <v>1.934853</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.799812</v>
+      </c>
+      <c r="I139" t="n">
+        <v>22.883439</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>90</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.437018</v>
+      </c>
+      <c r="C140" t="n">
+        <v>3.03255</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.941528</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.918351</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.5102950000000001</v>
+      </c>
+      <c r="G140" t="n">
+        <v>1.879585</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.816621</v>
+      </c>
+      <c r="I140" t="n">
+        <v>10.66957</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>183</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.405131</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.107024</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.918049</v>
+      </c>
+      <c r="E141" t="n">
+        <v>24.739925</v>
+      </c>
+      <c r="F141" t="n">
+        <v>26.359264</v>
+      </c>
+      <c r="G141" t="n">
+        <v>5.202134</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.379743</v>
+      </c>
+      <c r="I141" t="n">
+        <v>28.906181</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>113</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.389887</v>
+      </c>
+      <c r="C142" t="n">
+        <v>2.104427</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.906386</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1.22643</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.718132</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1.257969</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.55171</v>
+      </c>
+      <c r="I142" t="n">
+        <v>29.234477</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>89</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.37824</v>
+      </c>
+      <c r="C143" t="n">
+        <v>2.889001</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.897269</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.875483</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.450197</v>
+      </c>
+      <c r="G143" t="n">
+        <v>2.34899</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.909301</v>
+      </c>
+      <c r="I143" t="n">
+        <v>23.154762</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>186</v>
+      </c>
+      <c r="B144" t="n">
+        <v>0.370551</v>
+      </c>
+      <c r="C144" t="n">
+        <v>0.011682</v>
+      </c>
+      <c r="D144" t="n">
+        <v>0.8911480000000001</v>
+      </c>
+      <c r="E144" t="n">
+        <v>213.571085</v>
+      </c>
+      <c r="F144" t="n">
+        <v>795222.155427</v>
+      </c>
+      <c r="G144" t="n">
+        <v>4976.292026</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0.098523</v>
+      </c>
+      <c r="I144" t="n">
+        <v>26.418875</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>95</v>
+      </c>
+      <c r="B145" t="n">
+        <v>0.349543</v>
+      </c>
+      <c r="C145" t="n">
+        <v>2.630902</v>
+      </c>
+      <c r="D145" t="n">
+        <v>0.873979</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0.9121089999999999</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0.46741</v>
+      </c>
+      <c r="G145" t="n">
+        <v>2.015627</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0.781616</v>
+      </c>
+      <c r="I145" t="n">
+        <v>13.092093</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>94</v>
+      </c>
+      <c r="B146" t="n">
+        <v>0.346717</v>
+      </c>
+      <c r="C146" t="n">
+        <v>2.657166</v>
+      </c>
+      <c r="D146" t="n">
+        <v>0.871617</v>
+      </c>
+      <c r="E146" t="n">
+        <v>0.898219</v>
+      </c>
+      <c r="F146" t="n">
+        <v>0.445198</v>
+      </c>
+      <c r="G146" t="n">
+        <v>2.159289</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0.791332</v>
+      </c>
+      <c r="I146" t="n">
+        <v>18.347393</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>99</v>
+      </c>
+      <c r="B147" t="n">
+        <v>0.343668</v>
+      </c>
+      <c r="C147" t="n">
+        <v>2.579768</v>
+      </c>
+      <c r="D147" t="n">
+        <v>0.869055</v>
+      </c>
+      <c r="E147" t="n">
+        <v>0.919736</v>
+      </c>
+      <c r="F147" t="n">
+        <v>0.589222</v>
+      </c>
+      <c r="G147" t="n">
+        <v>1.855609</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0.729999</v>
+      </c>
+      <c r="I147" t="n">
+        <v>19.908026</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>116</v>
+      </c>
+      <c r="B148" t="n">
+        <v>0.336936</v>
+      </c>
+      <c r="C148" t="n">
+        <v>2.265032</v>
+      </c>
+      <c r="D148" t="n">
+        <v>0.8633420000000001</v>
+      </c>
+      <c r="E148" t="n">
+        <v>1.033812</v>
+      </c>
+      <c r="F148" t="n">
+        <v>0.725621</v>
+      </c>
+      <c r="G148" t="n">
+        <v>2.452768</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0.797409</v>
+      </c>
+      <c r="I148" t="n">
+        <v>18.195062</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>100</v>
+      </c>
+      <c r="B149" t="n">
+        <v>0.335885</v>
+      </c>
+      <c r="C149" t="n">
+        <v>2.510953</v>
+      </c>
+      <c r="D149" t="n">
+        <v>0.862444</v>
+      </c>
+      <c r="E149" t="n">
+        <v>0.930621</v>
+      </c>
+      <c r="F149" t="n">
+        <v>0.510022</v>
+      </c>
+      <c r="G149" t="n">
+        <v>1.758817</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0.7142810000000001</v>
+      </c>
+      <c r="I149" t="n">
+        <v>19.62056</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>98</v>
+      </c>
+      <c r="B150" t="n">
+        <v>0.330193</v>
+      </c>
+      <c r="C150" t="n">
+        <v>2.575389</v>
+      </c>
+      <c r="D150" t="n">
+        <v>0.857544</v>
+      </c>
+      <c r="E150" t="n">
+        <v>0.897056</v>
+      </c>
+      <c r="F150" t="n">
+        <v>0.514439</v>
+      </c>
+      <c r="G150" t="n">
+        <v>2.29165</v>
+      </c>
+      <c r="H150" t="n">
+        <v>0.821648</v>
+      </c>
+      <c r="I150" t="n">
+        <v>17.839741</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>102</v>
+      </c>
+      <c r="B151" t="n">
+        <v>0.326555</v>
+      </c>
+      <c r="C151" t="n">
+        <v>2.515723</v>
+      </c>
+      <c r="D151" t="n">
+        <v>0.854383</v>
+      </c>
+      <c r="E151" t="n">
+        <v>0.911575</v>
+      </c>
+      <c r="F151" t="n">
+        <v>0.551118</v>
+      </c>
+      <c r="G151" t="n">
+        <v>2.141025</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0.768589</v>
+      </c>
+      <c r="I151" t="n">
+        <v>17.48147</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>101</v>
+      </c>
+      <c r="B152" t="n">
+        <v>0.312211</v>
+      </c>
+      <c r="C152" t="n">
+        <v>2.430914</v>
+      </c>
+      <c r="D152" t="n">
+        <v>0.841685</v>
+      </c>
+      <c r="E152" t="n">
+        <v>0.9155450000000001</v>
+      </c>
+      <c r="F152" t="n">
+        <v>0.515491</v>
+      </c>
+      <c r="G152" t="n">
+        <v>2.11006</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0.741151</v>
+      </c>
+      <c r="I152" t="n">
+        <v>19.571152</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>96</v>
+      </c>
+      <c r="B153" t="n">
+        <v>0.267118</v>
+      </c>
+      <c r="C153" t="n">
+        <v>2.412568</v>
+      </c>
+      <c r="D153" t="n">
+        <v>0.7990390000000001</v>
+      </c>
+      <c r="E153" t="n">
+        <v>0.831393</v>
+      </c>
+      <c r="F153" t="n">
+        <v>0.491778</v>
+      </c>
+      <c r="G153" t="n">
+        <v>2.640349</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0.873509</v>
+      </c>
+      <c r="I153" t="n">
+        <v>11.110469</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>105</v>
+      </c>
+      <c r="B154" t="n">
+        <v>0.252463</v>
+      </c>
+      <c r="C154" t="n">
+        <v>2.149915</v>
+      </c>
+      <c r="D154" t="n">
+        <v>0.784151</v>
+      </c>
+      <c r="E154" t="n">
+        <v>0.898521</v>
+      </c>
+      <c r="F154" t="n">
+        <v>0.464173</v>
+      </c>
+      <c r="G154" t="n">
+        <v>2.199426</v>
+      </c>
+      <c r="H154" t="n">
+        <v>0.747876</v>
+      </c>
+      <c r="I154" t="n">
+        <v>11.263516</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>109</v>
+      </c>
+      <c r="B155" t="n">
+        <v>0.249664</v>
+      </c>
+      <c r="C155" t="n">
+        <v>2.112981</v>
+      </c>
+      <c r="D155" t="n">
+        <v>0.781242</v>
+      </c>
+      <c r="E155" t="n">
+        <v>0.907456</v>
+      </c>
+      <c r="F155" t="n">
+        <v>0.508992</v>
+      </c>
+      <c r="G155" t="n">
+        <v>1.977535</v>
+      </c>
+      <c r="H155" t="n">
+        <v>0.711749</v>
+      </c>
+      <c r="I155" t="n">
+        <v>21.789208</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>103</v>
+      </c>
+      <c r="B156" t="n">
+        <v>0.249333</v>
+      </c>
+      <c r="C156" t="n">
+        <v>2.17635</v>
+      </c>
+      <c r="D156" t="n">
+        <v>0.780897</v>
+      </c>
+      <c r="E156" t="n">
+        <v>0.880255</v>
+      </c>
+      <c r="F156" t="n">
+        <v>0.469133</v>
+      </c>
+      <c r="G156" t="n">
+        <v>2.288483</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0.753809</v>
+      </c>
+      <c r="I156" t="n">
+        <v>9.828652</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>108</v>
+      </c>
+      <c r="B157" t="n">
+        <v>0.246369</v>
+      </c>
+      <c r="C157" t="n">
+        <v>2.084478</v>
+      </c>
+      <c r="D157" t="n">
+        <v>0.777791</v>
+      </c>
+      <c r="E157" t="n">
+        <v>0.911755</v>
+      </c>
+      <c r="F157" t="n">
+        <v>0.512952</v>
+      </c>
+      <c r="G157" t="n">
+        <v>2.006343</v>
+      </c>
+      <c r="H157" t="n">
+        <v>0.694923</v>
+      </c>
+      <c r="I157" t="n">
+        <v>20.493297</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>111</v>
+      </c>
+      <c r="B158" t="n">
+        <v>0.233653</v>
+      </c>
+      <c r="C158" t="n">
+        <v>1.990373</v>
+      </c>
+      <c r="D158" t="n">
+        <v>0.764172</v>
+      </c>
+      <c r="E158" t="n">
+        <v>0.921717</v>
+      </c>
+      <c r="F158" t="n">
+        <v>0.523733</v>
+      </c>
+      <c r="G158" t="n">
+        <v>1.97597</v>
+      </c>
+      <c r="H158" t="n">
+        <v>0.653836</v>
+      </c>
+      <c r="I158" t="n">
+        <v>17.192231</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>110</v>
+      </c>
+      <c r="B159" t="n">
+        <v>0.231869</v>
+      </c>
+      <c r="C159" t="n">
+        <v>2.022648</v>
+      </c>
+      <c r="D159" t="n">
+        <v>0.762221</v>
+      </c>
+      <c r="E159" t="n">
+        <v>0.902385</v>
+      </c>
+      <c r="F159" t="n">
+        <v>0.494584</v>
+      </c>
+      <c r="G159" t="n">
+        <v>2.096608</v>
+      </c>
+      <c r="H159" t="n">
+        <v>0.696051</v>
+      </c>
+      <c r="I159" t="n">
+        <v>17.683452</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>106</v>
+      </c>
+      <c r="B160" t="n">
+        <v>0.220858</v>
+      </c>
+      <c r="C160" t="n">
+        <v>2.116466</v>
+      </c>
+      <c r="D160" t="n">
+        <v>0.74996</v>
+      </c>
+      <c r="E160" t="n">
+        <v>0.834862</v>
+      </c>
+      <c r="F160" t="n">
+        <v>0.433045</v>
+      </c>
+      <c r="G160" t="n">
+        <v>2.230883</v>
+      </c>
+      <c r="H160" t="n">
+        <v>0.774589</v>
+      </c>
+      <c r="I160" t="n">
+        <v>22.832527</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>112</v>
+      </c>
+      <c r="B161" t="n">
+        <v>0.217698</v>
+      </c>
+      <c r="C161" t="n">
+        <v>1.885562</v>
+      </c>
+      <c r="D161" t="n">
+        <v>0.746366</v>
+      </c>
+      <c r="E161" t="n">
+        <v>0.928138</v>
+      </c>
+      <c r="F161" t="n">
+        <v>0.54908</v>
+      </c>
+      <c r="G161" t="n">
+        <v>1.678983</v>
+      </c>
+      <c r="H161" t="n">
+        <v>0.618049</v>
+      </c>
+      <c r="I161" t="n">
+        <v>25.562456</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>166</v>
+      </c>
+      <c r="B162" t="n">
+        <v>0.211824</v>
+      </c>
+      <c r="C162" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="D162" t="n">
+        <v>0.739592</v>
+      </c>
+      <c r="E162" t="n">
+        <v>3.450682</v>
+      </c>
+      <c r="F162" t="n">
+        <v>4.36733</v>
+      </c>
+      <c r="G162" t="n">
+        <v>2.957989</v>
+      </c>
+      <c r="H162" t="n">
+        <v>0.372841</v>
+      </c>
+      <c r="I162" t="n">
+        <v>24.257191</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>126</v>
+      </c>
+      <c r="B163" t="n">
+        <v>0.20978</v>
+      </c>
+      <c r="C163" t="n">
+        <v>1.79108</v>
+      </c>
+      <c r="D163" t="n">
+        <v>0.737206</v>
+      </c>
+      <c r="E163" t="n">
+        <v>0.9532620000000001</v>
+      </c>
+      <c r="F163" t="n">
+        <v>0.54896</v>
+      </c>
+      <c r="G163" t="n">
+        <v>1.44139</v>
+      </c>
+      <c r="H163" t="n">
+        <v>0.509428</v>
+      </c>
+      <c r="I163" t="n">
+        <v>28.306273</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>118</v>
+      </c>
+      <c r="B164" t="n">
+        <v>0.203646</v>
+      </c>
+      <c r="C164" t="n">
+        <v>1.846008</v>
+      </c>
+      <c r="D164" t="n">
+        <v>0.729949</v>
+      </c>
+      <c r="E164" t="n">
+        <v>0.906778</v>
+      </c>
+      <c r="F164" t="n">
+        <v>0.5430199999999999</v>
+      </c>
+      <c r="G164" t="n">
+        <v>2.059599</v>
+      </c>
+      <c r="H164" t="n">
+        <v>0.656345</v>
+      </c>
+      <c r="I164" t="n">
+        <v>11.230696</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>117</v>
+      </c>
+      <c r="B165" t="n">
+        <v>0.19565</v>
+      </c>
+      <c r="C165" t="n">
+        <v>1.790534</v>
+      </c>
+      <c r="D165" t="n">
+        <v>0.720268</v>
+      </c>
+      <c r="E165" t="n">
+        <v>0.910239</v>
+      </c>
+      <c r="F165" t="n">
+        <v>0.490334</v>
+      </c>
+      <c r="G165" t="n">
+        <v>2.045991</v>
+      </c>
+      <c r="H165" t="n">
+        <v>0.633632</v>
+      </c>
+      <c r="I165" t="n">
+        <v>22.008935</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>124</v>
+      </c>
+      <c r="B166" t="n">
+        <v>0.189453</v>
+      </c>
+      <c r="C166" t="n">
+        <v>1.728261</v>
+      </c>
+      <c r="D166" t="n">
+        <v>0.712581</v>
+      </c>
+      <c r="E166" t="n">
+        <v>0.923015</v>
+      </c>
+      <c r="F166" t="n">
+        <v>0.524183</v>
+      </c>
+      <c r="G166" t="n">
+        <v>1.815225</v>
+      </c>
+      <c r="H166" t="n">
+        <v>0.603878</v>
+      </c>
+      <c r="I166" t="n">
+        <v>18.497292</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>127</v>
+      </c>
+      <c r="B167" t="n">
+        <v>0.188465</v>
+      </c>
+      <c r="C167" t="n">
+        <v>1.683618</v>
+      </c>
+      <c r="D167" t="n">
+        <v>0.71134</v>
+      </c>
+      <c r="E167" t="n">
+        <v>0.9441929999999999</v>
+      </c>
+      <c r="F167" t="n">
+        <v>0.471331</v>
+      </c>
+      <c r="G167" t="n">
+        <v>1.52467</v>
+      </c>
+      <c r="H167" t="n">
+        <v>0.535969</v>
+      </c>
+      <c r="I167" t="n">
+        <v>23.81923</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>128</v>
+      </c>
+      <c r="B168" t="n">
+        <v>0.18588</v>
+      </c>
+      <c r="C168" t="n">
+        <v>1.663367</v>
+      </c>
+      <c r="D168" t="n">
+        <v>0.708073</v>
+      </c>
+      <c r="E168" t="n">
+        <v>0.94693</v>
+      </c>
+      <c r="F168" t="n">
+        <v>0.543362</v>
+      </c>
+      <c r="G168" t="n">
+        <v>1.557196</v>
+      </c>
+      <c r="H168" t="n">
+        <v>0.5334370000000001</v>
+      </c>
+      <c r="I168" t="n">
+        <v>26.18775</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>121</v>
+      </c>
+      <c r="B169" t="n">
+        <v>0.185148</v>
+      </c>
+      <c r="C169" t="n">
+        <v>1.708095</v>
+      </c>
+      <c r="D169" t="n">
+        <v>0.707143</v>
+      </c>
+      <c r="E169" t="n">
+        <v>0.919712</v>
+      </c>
+      <c r="F169" t="n">
+        <v>0.493766</v>
+      </c>
+      <c r="G169" t="n">
+        <v>1.958493</v>
+      </c>
+      <c r="H169" t="n">
+        <v>0.580883</v>
+      </c>
+      <c r="I169" t="n">
+        <v>12.552069</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>119</v>
+      </c>
+      <c r="B170" t="n">
+        <v>0.181607</v>
+      </c>
+      <c r="C170" t="n">
+        <v>1.728465</v>
+      </c>
+      <c r="D170" t="n">
+        <v>0.702605</v>
+      </c>
+      <c r="E170" t="n">
+        <v>0.897245</v>
+      </c>
+      <c r="F170" t="n">
+        <v>0.470934</v>
+      </c>
+      <c r="G170" t="n">
+        <v>2.083808</v>
+      </c>
+      <c r="H170" t="n">
+        <v>0.649705</v>
+      </c>
+      <c r="I170" t="n">
+        <v>25.609201</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>179</v>
+      </c>
+      <c r="B171" t="n">
+        <v>0.181075</v>
+      </c>
+      <c r="C171" t="n">
+        <v>0.151215</v>
+      </c>
+      <c r="D171" t="n">
+        <v>0.701919</v>
+      </c>
+      <c r="E171" t="n">
+        <v>10.235994</v>
+      </c>
+      <c r="F171" t="n">
+        <v>21.120316</v>
+      </c>
+      <c r="G171" t="n">
+        <v>2.111177</v>
+      </c>
+      <c r="H171" t="n">
+        <v>0.196031</v>
+      </c>
+      <c r="I171" t="n">
+        <v>25.526151</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>133</v>
+      </c>
+      <c r="B172" t="n">
+        <v>0.170692</v>
+      </c>
+      <c r="C172" t="n">
+        <v>1.578676</v>
+      </c>
+      <c r="D172" t="n">
+        <v>0.688237</v>
+      </c>
+      <c r="E172" t="n">
+        <v>0.942613</v>
+      </c>
+      <c r="F172" t="n">
+        <v>0.558687</v>
+      </c>
+      <c r="G172" t="n">
+        <v>1.644217</v>
+      </c>
+      <c r="H172" t="n">
+        <v>0.538704</v>
+      </c>
+      <c r="I172" t="n">
+        <v>20.215942</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>114</v>
+      </c>
+      <c r="B173" t="n">
+        <v>0.168136</v>
+      </c>
+      <c r="C173" t="n">
+        <v>1.773535</v>
+      </c>
+      <c r="D173" t="n">
+        <v>0.6847839999999999</v>
+      </c>
+      <c r="E173" t="n">
+        <v>0.83065</v>
+      </c>
+      <c r="F173" t="n">
+        <v>0.367715</v>
+      </c>
+      <c r="G173" t="n">
+        <v>2.345184</v>
+      </c>
+      <c r="H173" t="n">
+        <v>0.709897</v>
+      </c>
+      <c r="I173" t="n">
+        <v>27.480933</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>125</v>
+      </c>
+      <c r="B174" t="n">
+        <v>0.165724</v>
+      </c>
+      <c r="C174" t="n">
+        <v>1.614372</v>
+      </c>
+      <c r="D174" t="n">
+        <v>0.681494</v>
+      </c>
+      <c r="E174" t="n">
+        <v>0.903797</v>
+      </c>
+      <c r="F174" t="n">
+        <v>0.386993</v>
+      </c>
+      <c r="G174" t="n">
+        <v>2.010438</v>
+      </c>
+      <c r="H174" t="n">
+        <v>0.614742</v>
+      </c>
+      <c r="I174" t="n">
+        <v>22.742359</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>132</v>
+      </c>
+      <c r="B175" t="n">
+        <v>0.151355</v>
+      </c>
+      <c r="C175" t="n">
+        <v>1.499891</v>
+      </c>
+      <c r="D175" t="n">
+        <v>0.661199</v>
+      </c>
+      <c r="E175" t="n">
+        <v>0.915704</v>
+      </c>
+      <c r="F175" t="n">
+        <v>0.507256</v>
+      </c>
+      <c r="G175" t="n">
+        <v>1.766455</v>
+      </c>
+      <c r="H175" t="n">
+        <v>0.556786</v>
+      </c>
+      <c r="I175" t="n">
+        <v>21.849049</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>122</v>
+      </c>
+      <c r="B176" t="n">
+        <v>0.149368</v>
+      </c>
+      <c r="C176" t="n">
+        <v>1.592837</v>
+      </c>
+      <c r="D176" t="n">
+        <v>0.658293</v>
+      </c>
+      <c r="E176" t="n">
+        <v>0.854706</v>
+      </c>
+      <c r="F176" t="n">
+        <v>0.387413</v>
+      </c>
+      <c r="G176" t="n">
+        <v>2.156552</v>
+      </c>
+      <c r="H176" t="n">
+        <v>0.637643</v>
+      </c>
+      <c r="I176" t="n">
+        <v>20.165783</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>115</v>
+      </c>
+      <c r="B177" t="n">
+        <v>0.147515</v>
+      </c>
+      <c r="C177" t="n">
+        <v>1.649913</v>
+      </c>
+      <c r="D177" t="n">
+        <v>0.65556</v>
+      </c>
+      <c r="E177" t="n">
+        <v>0.818303</v>
+      </c>
+      <c r="F177" t="n">
+        <v>0.387863</v>
+      </c>
+      <c r="G177" t="n">
+        <v>2.832938</v>
+      </c>
+      <c r="H177" t="n">
+        <v>0.755547</v>
+      </c>
+      <c r="I177" t="n">
+        <v>8.944533</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>188</v>
+      </c>
+      <c r="B178" t="n">
+        <v>0.147379</v>
+      </c>
+      <c r="C178" t="n">
+        <v>0.003999</v>
+      </c>
+      <c r="D178" t="n">
+        <v>0.655359</v>
+      </c>
+      <c r="E178" t="n">
+        <v>337.425317</v>
+      </c>
+      <c r="F178" t="n">
+        <v>167493.375485</v>
+      </c>
+      <c r="G178" t="n">
+        <v>1257.271454</v>
+      </c>
+      <c r="H178" t="n">
+        <v>0.156467</v>
+      </c>
+      <c r="I178" t="n">
+        <v>29.358757</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>136</v>
+      </c>
+      <c r="B179" t="n">
+        <v>0.146783</v>
+      </c>
+      <c r="C179" t="n">
+        <v>1.481214</v>
+      </c>
+      <c r="D179" t="n">
+        <v>0.654475</v>
+      </c>
+      <c r="E179" t="n">
+        <v>0.908484</v>
+      </c>
+      <c r="F179" t="n">
+        <v>0.536127</v>
+      </c>
+      <c r="G179" t="n">
+        <v>2.126991</v>
+      </c>
+      <c r="H179" t="n">
+        <v>0.58756</v>
+      </c>
+      <c r="I179" t="n">
+        <v>26.190429</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>187</v>
+      </c>
+      <c r="B180" t="n">
+        <v>0.143796</v>
+      </c>
+      <c r="C180" t="n">
+        <v>0.004956</v>
+      </c>
+      <c r="D180" t="n">
+        <v>0.6500050000000001</v>
+      </c>
+      <c r="E180" t="n">
+        <v>267.845818</v>
+      </c>
+      <c r="F180" t="n">
+        <v>19489.310332</v>
+      </c>
+      <c r="G180" t="n">
+        <v>3417.471452</v>
+      </c>
+      <c r="H180" t="n">
+        <v>0.211703</v>
+      </c>
+      <c r="I180" t="n">
+        <v>29.538132</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>138</v>
+      </c>
+      <c r="B181" t="n">
+        <v>0.143133</v>
+      </c>
+      <c r="C181" t="n">
+        <v>1.399429</v>
+      </c>
+      <c r="D181" t="n">
+        <v>0.649003</v>
+      </c>
+      <c r="E181" t="n">
+        <v>0.945567</v>
+      </c>
+      <c r="F181" t="n">
+        <v>0.490662</v>
+      </c>
+      <c r="G181" t="n">
+        <v>1.494409</v>
+      </c>
+      <c r="H181" t="n">
+        <v>0.488563</v>
+      </c>
+      <c r="I181" t="n">
+        <v>17.752264</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>135</v>
+      </c>
+      <c r="B182" t="n">
+        <v>0.143049</v>
+      </c>
+      <c r="C182" t="n">
+        <v>1.465363</v>
+      </c>
+      <c r="D182" t="n">
+        <v>0.648876</v>
+      </c>
+      <c r="E182" t="n">
+        <v>0.902668</v>
+      </c>
+      <c r="F182" t="n">
+        <v>0.466367</v>
+      </c>
+      <c r="G182" t="n">
+        <v>1.891385</v>
+      </c>
+      <c r="H182" t="n">
+        <v>0.5830650000000001</v>
+      </c>
+      <c r="I182" t="n">
+        <v>20.578329</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>131</v>
+      </c>
+      <c r="B183" t="n">
+        <v>0.139398</v>
+      </c>
+      <c r="C183" t="n">
+        <v>1.435275</v>
+      </c>
+      <c r="D183" t="n">
+        <v>0.643309</v>
+      </c>
+      <c r="E183" t="n">
+        <v>0.905844</v>
+      </c>
+      <c r="F183" t="n">
+        <v>0.5599460000000001</v>
+      </c>
+      <c r="G183" t="n">
+        <v>1.849042</v>
+      </c>
+      <c r="H183" t="n">
+        <v>0.5644479999999999</v>
+      </c>
+      <c r="I183" t="n">
+        <v>20.573014</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>160</v>
+      </c>
+      <c r="B184" t="n">
+        <v>0.132361</v>
+      </c>
+      <c r="C184" t="n">
+        <v>0.669922</v>
+      </c>
+      <c r="D184" t="n">
+        <v>0.632296</v>
+      </c>
+      <c r="E184" t="n">
+        <v>1.874853</v>
+      </c>
+      <c r="F184" t="n">
+        <v>1.242254</v>
+      </c>
+      <c r="G184" t="n">
+        <v>3.058602</v>
+      </c>
+      <c r="H184" t="n">
+        <v>0.434878</v>
+      </c>
+      <c r="I184" t="n">
+        <v>22.733085</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>137</v>
+      </c>
+      <c r="B185" t="n">
+        <v>0.124995</v>
+      </c>
+      <c r="C185" t="n">
+        <v>1.388327</v>
+      </c>
+      <c r="D185" t="n">
+        <v>0.6203419999999999</v>
+      </c>
+      <c r="E185" t="n">
+        <v>0.870804</v>
+      </c>
+      <c r="F185" t="n">
+        <v>0.537647</v>
+      </c>
+      <c r="G185" t="n">
+        <v>2.56728</v>
+      </c>
+      <c r="H185" t="n">
+        <v>0.6034890000000001</v>
+      </c>
+      <c r="I185" t="n">
+        <v>18.904369</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>145</v>
+      </c>
+      <c r="B186" t="n">
+        <v>0.11414</v>
+      </c>
+      <c r="C186" t="n">
+        <v>1.233245</v>
+      </c>
+      <c r="D186" t="n">
+        <v>0.601838</v>
+      </c>
+      <c r="E186" t="n">
+        <v>0.922698</v>
+      </c>
+      <c r="F186" t="n">
+        <v>0.547832</v>
+      </c>
+      <c r="G186" t="n">
+        <v>1.780257</v>
+      </c>
+      <c r="H186" t="n">
+        <v>0.496122</v>
+      </c>
+      <c r="I186" t="n">
+        <v>24.763818</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>129</v>
+      </c>
+      <c r="B187" t="n">
+        <v>0.112914</v>
+      </c>
+      <c r="C187" t="n">
+        <v>1.345512</v>
+      </c>
+      <c r="D187" t="n">
+        <v>0.599675</v>
+      </c>
+      <c r="E187" t="n">
+        <v>0.839642</v>
+      </c>
+      <c r="F187" t="n">
+        <v>0.392841</v>
+      </c>
+      <c r="G187" t="n">
+        <v>2.293112</v>
+      </c>
+      <c r="H187" t="n">
+        <v>0.610822</v>
+      </c>
+      <c r="I187" t="n">
+        <v>9.053782999999999</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>146</v>
+      </c>
+      <c r="B188" t="n">
+        <v>0.110899</v>
+      </c>
+      <c r="C188" t="n">
+        <v>1.173013</v>
+      </c>
+      <c r="D188" t="n">
+        <v>0.596087</v>
+      </c>
+      <c r="E188" t="n">
+        <v>0.951624</v>
+      </c>
+      <c r="F188" t="n">
+        <v>0.509388</v>
+      </c>
+      <c r="G188" t="n">
+        <v>1.473153</v>
+      </c>
+      <c r="H188" t="n">
+        <v>0.424566</v>
+      </c>
+      <c r="I188" t="n">
+        <v>26.568698</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>158</v>
+      </c>
+      <c r="B189" t="n">
+        <v>0.1099</v>
+      </c>
+      <c r="C189" t="n">
+        <v>0.915708</v>
+      </c>
+      <c r="D189" t="n">
+        <v>0.594291</v>
+      </c>
+      <c r="E189" t="n">
+        <v>1.21169</v>
+      </c>
+      <c r="F189" t="n">
+        <v>0.830635</v>
+      </c>
+      <c r="G189" t="n">
+        <v>3.390961</v>
+      </c>
+      <c r="H189" t="n">
+        <v>0.508645</v>
+      </c>
+      <c r="I189" t="n">
+        <v>19.982511</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>147</v>
+      </c>
+      <c r="B190" t="n">
+        <v>0.106259</v>
+      </c>
+      <c r="C190" t="n">
+        <v>1.152663</v>
+      </c>
+      <c r="D190" t="n">
+        <v>0.587654</v>
+      </c>
+      <c r="E190" t="n">
+        <v>0.9412199999999999</v>
+      </c>
+      <c r="F190" t="n">
+        <v>0.561492</v>
+      </c>
+      <c r="G190" t="n">
+        <v>1.7058</v>
+      </c>
+      <c r="H190" t="n">
+        <v>0.475633</v>
+      </c>
+      <c r="I190" t="n">
+        <v>25.187036</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
